--- a/docagent_clean_mvp/sample_data/raw_excels/NIST_SetB.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/NIST_SetB.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A formal Incident Response Plan defines roles, escalation paths, and a 24-hour notification requirement for confirmed breaches.</t>
+          <t>Standard Respond function control mandates that a formal Incident Response Plan defines roles, escalation paths, and a 24-hour notification requirement for confirmed breaches. [NIST-045]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Compliant - IR plan last tested this quarter</t>
+          <t>Compliant - evidence on file</t>
         </is>
       </c>
     </row>
